--- a/data/trans_orig/P1433-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1433-Edad-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de esterilidad en 2012</t>
+          <t>Población con diagnóstico de esterilidad en 2012 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,97 +731,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1951</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1957</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1957</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>452195</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>454146</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>427310</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>429267</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>881456</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>883413</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5489</t>
+          <t>6232</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,62 +1109,62 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1094</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>5521</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1094</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>5444</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>681598</t>
+          <t>680855</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>608207</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>610255</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1291898</t>
+          <t>1291821</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>932</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9268</t>
+          <t>9384</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7381</t>
+          <t>7370</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12204</t>
+          <t>12410</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>672595</t>
+          <t>672479</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>680938</t>
+          <t>680931</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>702193</t>
+          <t>702204</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1379233</t>
+          <t>1379027</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1388725</t>
+          <t>1389434</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2149</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>948</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7851</t>
+          <t>7835</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>954</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7825</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>612468</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>614617</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>606413</t>
+          <t>606429</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>613306</t>
+          <t>613316</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1221055</t>
+          <t>1221052</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1227922</t>
+          <t>1227926</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -2103,97 +2103,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1045</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2092</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5190</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>1045</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5253</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>4225</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1045</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>5827</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>427337</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>429429</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>442547</t>
+          <t>442610</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>871402</t>
+          <t>873004</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2446,82 +2446,82 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>2101</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5153</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>902</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5416</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>902</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4567</t>
+          <t>4586</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>307685</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>309786</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>348580</t>
+          <t>348843</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>659215</t>
+          <t>659196</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,67 +2804,67 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>3338</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>1079</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>9376</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
           <t>0,86%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>3338</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>10058</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>3338</t>
-        </is>
-      </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>9875</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>247701</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>249851</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,42 +2917,42 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>384532</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>378494</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>386791</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
           <t>99,14%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>346</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>384532</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>377812</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>386790</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,14%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>628697</t>
+          <t>627846</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>636658</t>
+          <t>636640</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1799</t>
+          <t>1819</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9708</t>
+          <t>10397</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5087</t>
+          <t>5247</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18645</t>
+          <t>18754</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8253</t>
+          <t>8737</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23631</t>
+          <t>24007</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3417071</t>
+          <t>3416382</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3424980</t>
+          <t>3424960</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3534381</t>
+          <t>3534272</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3547939</t>
+          <t>3547779</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6956174</t>
+          <t>6955798</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6971552</t>
+          <t>6971068</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de esterilidad en 2016</t>
+          <t>Población con diagnóstico de esterilidad en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3710,97 +3710,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1876</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>417419</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>419463</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>393879</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>395755</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>813256</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>815218</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4053,97 +4053,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1866</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>1932</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>588500</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>590496</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>561678</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>563544</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1152108</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1154040</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6131</t>
+          <t>5369</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4431,62 +4431,62 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1072</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1907</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>5706</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1072</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>5400</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>662966</t>
+          <t>663728</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>659479</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>661386</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1325083</t>
+          <t>1324777</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4739,97 +4739,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2128</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5662</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1020</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5786</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>5115</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1020</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>5126</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>643920</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>646048</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>643291</t>
+          <t>643415</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1289999</t>
+          <t>1290010</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5082,97 +5082,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2159</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2198</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>2182</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>475759</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>477918</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>494651</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>496849</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>972585</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>974767</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5425,97 +5425,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1969</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5096</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>1020</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5149</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>5126</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1020</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>5302</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>332361</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>334330</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>372613</t>
+          <t>372666</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>706790</t>
+          <t>706966</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5432</t>
+          <t>6973</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5803,62 +5803,62 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>1802</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2543</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>7211</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1802</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>6501</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>251566</t>
+          <t>250025</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>397626</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>400169</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>650666</t>
+          <t>649956</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>890</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7708</t>
+          <t>8072</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>1838</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11137</t>
+          <t>11423</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3386642</t>
+          <t>3386278</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3393459</t>
+          <t>3393460</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6239,7 +6239,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3538135</t>
+          <t>3537421</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -6274,7 +6274,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6927755</t>
+          <t>6927469</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6937064</t>
+          <t>6937054</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">

--- a/data/trans_orig/P1433-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1433-Edad-trans_orig.xlsx
@@ -1079,7 +1079,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>6316</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5521</t>
+          <t>5453</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>680855</t>
+          <t>680771</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1291821</t>
+          <t>1291889</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>938</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9384</t>
+          <t>8466</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7370</t>
+          <t>6386</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12410</t>
+          <t>12099</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>672479</t>
+          <t>673397</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>680931</t>
+          <t>680925</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>702204</t>
+          <t>703188</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1379027</t>
+          <t>1379338</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1389434</t>
+          <t>1388634</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7835</t>
+          <t>8630</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>951</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7828</t>
+          <t>7796</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>606429</t>
+          <t>605634</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1221052</t>
+          <t>1221084</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1227926</t>
+          <t>1227929</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>4968</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4225</t>
+          <t>5853</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>442610</t>
+          <t>442832</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>873004</t>
+          <t>871376</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5153</t>
+          <t>5455</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4586</t>
+          <t>4532</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>348843</t>
+          <t>348541</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>659196</t>
+          <t>659250</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1079</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9376</t>
+          <t>8896</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9875</t>
+          <t>8836</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>378494</t>
+          <t>378974</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>386791</t>
+          <t>386782</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>627846</t>
+          <t>628885</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>636640</t>
+          <t>636644</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1819</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10397</t>
+          <t>12269</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5247</t>
+          <t>4964</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18754</t>
+          <t>18089</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8737</t>
+          <t>9073</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>24007</t>
+          <t>23435</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3416382</t>
+          <t>3414510</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3424960</t>
+          <t>3424937</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3534272</t>
+          <t>3534937</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3547779</t>
+          <t>3548062</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6955798</t>
+          <t>6956370</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6971068</t>
+          <t>6970732</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5369</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5706</t>
+          <t>5988</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>663728</t>
+          <t>662687</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1324777</t>
+          <t>1324495</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4779,7 +4779,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5662</t>
+          <t>5115</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5115</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -4887,7 +4887,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>643415</t>
+          <t>643962</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1290010</t>
+          <t>1288980</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5096</t>
+          <t>5924</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5126</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>372666</t>
+          <t>371838</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>706966</t>
+          <t>706961</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6973</t>
+          <t>6256</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7211</t>
+          <t>6306</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>250025</t>
+          <t>250742</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>649956</t>
+          <t>650861</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>888</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8072</t>
+          <t>7582</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>7126</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>1823</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11423</t>
+          <t>10260</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
     </row>
@@ -6224,12 +6224,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3386278</t>
+          <t>3386768</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3393460</t>
+          <t>3393462</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6239,7 +6239,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3537421</t>
+          <t>3537416</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6927469</t>
+          <t>6928632</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6937054</t>
+          <t>6937069</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
